--- a/JADWAL.xlsx
+++ b/JADWAL.xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -183,6 +183,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,7 +524,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -535,7 +538,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -549,7 +552,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -563,7 +566,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -577,7 +580,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -591,7 +594,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7" s="4">
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -605,7 +608,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8" s="4">
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">

--- a/JADWAL.xlsx
+++ b/JADWAL.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Minggu</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Deployment &amp; Training</t>
-  </si>
-  <si>
-    <t>Maintenance Awal</t>
   </si>
   <si>
     <t>- Launching ke domain resmi
@@ -68,11 +65,6 @@
 - Training admin internal</t>
   </si>
   <si>
-    <t>- Monitoring performa
-- Backup rutin
-- Evaluasi feedback pengguna</t>
-  </si>
-  <si>
     <t>Dokumen kebutuhan &amp; struktur web</t>
   </si>
   <si>
@@ -89,15 +81,6 @@
   </si>
   <si>
     <t>Web live &amp; siap digunakan</t>
-  </si>
-  <si>
-    <t>Web terjaga &amp; optimal</t>
-  </si>
-  <si>
-    <t>3–4</t>
-  </si>
-  <si>
-    <t>5–6</t>
   </si>
   <si>
     <t>-Uji fungsionalitas &amp; kompatibilitas
@@ -124,7 +107,16 @@
 - Fitur kontak &amp; admin panel</t>
   </si>
   <si>
-    <t>7–8</t>
+    <t>2–3</t>
+  </si>
+  <si>
+    <t>4–5</t>
+  </si>
+  <si>
+    <t>6–7</t>
+  </si>
+  <si>
+    <t>8–9</t>
   </si>
 </sst>
 </file>
@@ -493,7 +485,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -501,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -531,94 +523,80 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/JADWAL.xlsx
+++ b/JADWAL.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Minggu</t>
   </si>
@@ -117,6 +117,27 @@
   </si>
   <si>
     <t>8–9</t>
+  </si>
+  <si>
+    <t>Planning Date</t>
+  </si>
+  <si>
+    <t>8 Mei 2026</t>
+  </si>
+  <si>
+    <t>15 &amp; 22 Mei 2026</t>
+  </si>
+  <si>
+    <t>29 Mei &amp; 5 Juni 2026</t>
+  </si>
+  <si>
+    <t>12 Juni &amp; 19 Juni 2026</t>
+  </si>
+  <si>
+    <t>10 Juli 2026</t>
+  </si>
+  <si>
+    <t>26 Juni &amp; 3 Juli 2026</t>
   </si>
 </sst>
 </file>
@@ -132,12 +153,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -167,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -179,6 +206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,109 +521,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
